--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535240441</v>
+        <v>46157.93108206213</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108206213</v>
+        <v>46157.93364511682</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93364511682</v>
+        <v>46157.93665141083</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93665141083</v>
+        <v>46158.28191029232</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28191029232</v>
+        <v>46158.2970878255</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2970878255</v>
+        <v>46158.29785546964</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29785546964</v>
+        <v>46158.33352239231</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352239231</v>
+        <v>46158.37208704162</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.1_Исковые_документы_и_комплекты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37208704162</v>
+        <v>46158.37424637867</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
